--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57820</v>
+        <v>57846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57846</v>
+        <v>57848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>57906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57906</v>
+        <v>57908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25025-2021 artfynd.xlsx
+++ b/artfynd/A 25025-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191587</v>
       </c>
       <c r="B2" t="n">
-        <v>57908</v>
+        <v>57942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
